--- a/data/trans_bre/IP1008-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1008-Edad-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 0,0</t>
+          <t>-2,9; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,87</t>
+          <t>-1,46; 0,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,48</t>
+          <t>-1,34; 0,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 0,41</t>
+          <t>-2,41; 0,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 3,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,29</t>
+          <t>0,33; 3,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,48</t>
+          <t>-0,32; 2,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,63; -0,36</t>
+          <t>-3,35; -0,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,27</t>
+          <t>-1,59; 2,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,51</t>
+          <t>-0,77; 0,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,72</t>
+          <t>-0,5; 0,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,43</t>
+          <t>0,02; 1,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-83,19; 272,56</t>
+          <t>-80,27; 210,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,1; 473,16</t>
+          <t>-79,17; 424,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-33,42; 1875,83</t>
+          <t>-14,44; 1713,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1008-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1008-Edad-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 0,0</t>
+          <t>-3,33; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,87</t>
+          <t>-1,45; 0,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,49</t>
+          <t>-1,35; 0,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,82</t>
+          <t>-2,45; 0,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 3,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,6</t>
+          <t>0,32; 3,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,41</t>
+          <t>-0,32; 2,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,35; -0,36</t>
+          <t>-3,65; -0,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,24</t>
+          <t>-1,43; 2,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,78; —</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,53</t>
+          <t>-0,73; 0,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,69</t>
+          <t>-0,49; 0,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,36</t>
+          <t>0,04; 1,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-80,27; 210,14</t>
+          <t>-79,88; 306,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-79,17; 424,2</t>
+          <t>-75,15; 536,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 1713,97</t>
+          <t>-35,51; 1377,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1008-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1008-Edad-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 0,0</t>
+          <t>-3,26; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,5</t>
+          <t>-1,35; 0,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 0,77</t>
+          <t>-2,9; 0,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,45</t>
+          <t>-0,33; 2,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,65; -0,37</t>
+          <t>-3,63; -0,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,5</t>
+          <t>-1,49; 2,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,78; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,57</t>
+          <t>-0,75; 0,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,74</t>
+          <t>-0,42; 0,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,38</t>
+          <t>0,07; 1,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-79,88; 306,65</t>
+          <t>-83,19; 272,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-75,15; 536,77</t>
+          <t>-74,1; 473,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-35,51; 1377,3</t>
+          <t>-33,42; 1875,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1008-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1008-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,137 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-8,08%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>-0.5806851206598709</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.03767178636941999</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.08076658817006389</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,26; 0,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-1,45; 0,87</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.261223171993596</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.450901481696227</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.8685352965873715</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,28</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,63</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-52,65%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,35; 0,48</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,21</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,27</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+      <c r="C7" s="5" t="n">
+        <v>-0.2817872506661548</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.6313307320377793</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.6532223575585442</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.5264585432753404</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,9</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-56,98%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.347998371182185</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,9; 0,41</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,83</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,32; 3,29</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.4767478670040526</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.210357850830191</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.27469322613843</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,34 +741,26 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,73</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,46</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>220,56%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>31,25%</t>
+      <c r="C10" s="5" t="n">
+        <v>-0.5469318873831763</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.897871456060567</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.22427401976708</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0.5697831060833393</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -869,122 +768,198 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,33; 2,48</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,63; -0,36</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,49; 2,27</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.898889302899795</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.3226120814161185</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.4137428245024308</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.829846620643146</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.290140651513294</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.7273835780865964</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.45705043067496</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.3499481528600464</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2.205581425607449</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.3125438631442148</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.3289083542629518</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.628059143590205</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.492458090082948</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.476195694060096</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-0.3644049878173788</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.272607700743055</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,62</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-16,67%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>13,3%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>238,31%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,75; 0,51</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-0,42; 0,72</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 1,43</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-83,19; 272,56</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-74,1; 473,16</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-33,42; 1875,83</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.09456870809815381</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.05809862058249191</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.6235032650964726</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.1666542199213103</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.133046588432546</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>2.383106017031267</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.746692449835114</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.4228404552701995</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.07309033073290359</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.8319000694290843</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.7409585741499151</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3342067075180221</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.5064903933416419</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.7206275644707789</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.425982180308536</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>2.725627076927594</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>4.731594453655177</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>18.75831682807075</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +968,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
